--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N52_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N52_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.17514255297625</v>
+        <v>7.503460664858641</v>
       </c>
       <c r="D2" t="n">
-        <v>45.41874283573344</v>
+        <v>7.380545710806684</v>
       </c>
       <c r="E2" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F2" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.47527844146212</v>
+        <v>7.389732746737594</v>
       </c>
       <c r="D3" t="n">
-        <v>44.50492305596706</v>
+        <v>7.232049996594648</v>
       </c>
       <c r="E3" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F3" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>43.3924637577553</v>
+        <v>7.051275360635237</v>
       </c>
       <c r="D4" t="n">
-        <v>42.91924534539129</v>
+        <v>6.974377368626085</v>
       </c>
       <c r="E4" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F4" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>59.47782071354496</v>
+        <v>9.665145865951057</v>
       </c>
       <c r="D5" t="n">
-        <v>59.69405228906875</v>
+        <v>9.700283496973672</v>
       </c>
       <c r="E5" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F5" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.97403477473495</v>
+        <v>4.383280650894429</v>
       </c>
       <c r="D6" t="n">
-        <v>26.21712391220487</v>
+        <v>4.260282635733291</v>
       </c>
       <c r="E6" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F6" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>52.39483556001523</v>
+        <v>8.514160778502475</v>
       </c>
       <c r="D7" t="n">
-        <v>51.44100443321119</v>
+        <v>8.35916322039682</v>
       </c>
       <c r="E7" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F7" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.75899991967673</v>
+        <v>5.810837486947468</v>
       </c>
       <c r="D8" t="n">
-        <v>35.90527826832936</v>
+        <v>5.834607718603522</v>
       </c>
       <c r="E8" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F8" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>33.03561425870367</v>
+        <v>5.368287317039346</v>
       </c>
       <c r="D9" t="n">
-        <v>32.14124605034785</v>
+        <v>5.222952483181525</v>
       </c>
       <c r="E9" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F9" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>36.71239263101641</v>
+        <v>5.965763802540168</v>
       </c>
       <c r="D10" t="n">
-        <v>37.23636787477815</v>
+        <v>6.050909779651449</v>
       </c>
       <c r="E10" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F10" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>24.67179893341748</v>
+        <v>4.009167326680341</v>
       </c>
       <c r="D11" t="n">
-        <v>25.38599908498487</v>
+        <v>4.125224851310041</v>
       </c>
       <c r="E11" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F11" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.3786319956765</v>
+        <v>6.236527699297431</v>
       </c>
       <c r="D12" t="n">
-        <v>39.14934367881407</v>
+        <v>6.361768347807287</v>
       </c>
       <c r="E12" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F12" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.17570538385799</v>
+        <v>7.991052124876925</v>
       </c>
       <c r="D13" t="n">
-        <v>49.34065261019558</v>
+        <v>8.017856049156782</v>
       </c>
       <c r="E13" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F13" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>21.19828335359979</v>
+        <v>3.444721044959967</v>
       </c>
       <c r="D14" t="n">
-        <v>22.21224263823914</v>
+        <v>3.60948942871386</v>
       </c>
       <c r="E14" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F14" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.88469347902923</v>
+        <v>6.15626269034225</v>
       </c>
       <c r="D15" t="n">
-        <v>38.07886552931954</v>
+        <v>6.187815648514426</v>
       </c>
       <c r="E15" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F15" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>45.23732621665291</v>
+        <v>7.351065510206098</v>
       </c>
       <c r="D16" t="n">
-        <v>46.14734610231073</v>
+        <v>7.498943741625493</v>
       </c>
       <c r="E16" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F16" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>25.50761383957974</v>
+        <v>4.144987248931708</v>
       </c>
       <c r="D17" t="n">
-        <v>25.52472433141869</v>
+        <v>4.147767703855537</v>
       </c>
       <c r="E17" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F17" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>21.34929368766208</v>
+        <v>3.469260224245089</v>
       </c>
       <c r="D18" t="n">
-        <v>21.13629357133837</v>
+        <v>3.434647705342485</v>
       </c>
       <c r="E18" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F18" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>39.1970075850189</v>
+        <v>6.369513732565572</v>
       </c>
       <c r="D19" t="n">
-        <v>39.02762359688364</v>
+        <v>6.341988834493592</v>
       </c>
       <c r="E19" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F19" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.94263978762576</v>
+        <v>3.890678965489186</v>
       </c>
       <c r="D20" t="n">
-        <v>23.50531854708632</v>
+        <v>3.819614263901527</v>
       </c>
       <c r="E20" t="n">
-        <v>10.83206592292239</v>
+        <v>1.760210712474889</v>
       </c>
       <c r="F20" t="n">
-        <v>10.7399710508956</v>
+        <v>1.745245295770534</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
